--- a/Externallibrary/tools/excelToJson/xlsx/旧货翻身局_配置数据.xlsx
+++ b/Externallibrary/tools/excelToJson/xlsx/旧货翻身局_配置数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ITEM_DEFS" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
     <t>bronze</t>
   </si>
   <si>
-    <t>金属</t>
+    <t>金</t>
   </si>
   <si>
     <t>item_14</t>
@@ -252,7 +252,7 @@
     <t>旧砚台</t>
   </si>
   <si>
-    <t>杂项</t>
+    <t>杂</t>
   </si>
   <si>
     <t>item_23</t>
@@ -318,7 +318,7 @@
     <t>folkToy</t>
   </si>
   <si>
-    <t>布皮</t>
+    <t>布</t>
   </si>
   <si>
     <t>item_32</t>
@@ -1045,7 +1045,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1067,6 +1067,12 @@
       <sz val="11"/>
       <color rgb="FF2D2018"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2D2018"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1712,153 +1718,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1898,6 +1904,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2200,13 +2209,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ITEM_DEFSTable" displayName="ITEM_DEFSTable" ref="A2:H103" totalsRowShown="0">
   <tableColumns count="8">
@@ -2445,7 +2447,7 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="15" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2513,10 +2515,10 @@
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="21" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -2539,10 +2541,10 @@
       <c r="E4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="22">
         <v>180</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="22">
         <v>1</v>
       </c>
       <c r="H4" s="14" t="s">
@@ -2565,10 +2567,10 @@
       <c r="E5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <v>420</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="22">
         <v>3</v>
       </c>
       <c r="H5" s="14" t="s">
@@ -2591,10 +2593,10 @@
       <c r="E6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>360</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="22">
         <v>2</v>
       </c>
       <c r="H6" s="14" t="s">
@@ -2617,10 +2619,10 @@
       <c r="E7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <v>260</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <v>2</v>
       </c>
       <c r="H7" s="14" t="s">
@@ -2643,10 +2645,10 @@
       <c r="E8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <v>320</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <v>2</v>
       </c>
       <c r="H8" s="14" t="s">
@@ -2669,10 +2671,10 @@
       <c r="E9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <v>210</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <v>1</v>
       </c>
       <c r="H9" s="14" t="s">
@@ -2695,10 +2697,10 @@
       <c r="E10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="22">
         <v>520</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <v>3</v>
       </c>
       <c r="H10" s="14" t="s">
@@ -2721,10 +2723,10 @@
       <c r="E11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>280</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="22">
         <v>2</v>
       </c>
       <c r="H11" s="14" t="s">
@@ -2747,10 +2749,10 @@
       <c r="E12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <v>460</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <v>3</v>
       </c>
       <c r="H12" s="14" t="s">
@@ -2773,10 +2775,10 @@
       <c r="E13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="22">
         <v>380</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="22">
         <v>3</v>
       </c>
       <c r="H13" s="14" t="s">
@@ -2799,10 +2801,10 @@
       <c r="E14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <v>330</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <v>2</v>
       </c>
       <c r="H14" s="14" t="s">
@@ -2825,10 +2827,10 @@
       <c r="E15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <v>260</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="22">
         <v>2</v>
       </c>
       <c r="H15" s="14" t="s">
@@ -2848,13 +2850,13 @@
       <c r="D16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="22">
         <v>480</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <v>4</v>
       </c>
       <c r="H16" s="14" t="s">
@@ -2874,13 +2876,13 @@
       <c r="D17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>160</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="22">
         <v>1</v>
       </c>
       <c r="H17" s="14" t="s">
@@ -2900,13 +2902,13 @@
       <c r="D18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="22">
         <v>300</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="22">
         <v>2</v>
       </c>
       <c r="H18" s="14" t="s">
@@ -2926,13 +2928,13 @@
       <c r="D19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="22">
         <v>220</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="22">
         <v>1</v>
       </c>
       <c r="H19" s="14" t="s">
@@ -2952,13 +2954,13 @@
       <c r="D20" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="22">
         <v>350</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="22">
         <v>3</v>
       </c>
       <c r="H20" s="14" t="s">
@@ -2978,13 +2980,13 @@
       <c r="D21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="22">
         <v>240</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="22">
         <v>2</v>
       </c>
       <c r="H21" s="14" t="s">
@@ -3007,10 +3009,10 @@
       <c r="E22" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="22">
         <v>300</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="22">
         <v>3</v>
       </c>
       <c r="H22" s="14" t="s">
@@ -3033,10 +3035,10 @@
       <c r="E23" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="22">
         <v>360</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="22">
         <v>4</v>
       </c>
       <c r="H23" s="14" t="s">
@@ -3059,10 +3061,10 @@
       <c r="E24" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="22">
         <v>260</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="22">
         <v>2</v>
       </c>
       <c r="H24" s="14" t="s">
@@ -3082,13 +3084,13 @@
       <c r="D25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="22">
         <v>240</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="22">
         <v>2</v>
       </c>
       <c r="H25" s="14" t="s">
@@ -3111,10 +3113,10 @@
       <c r="E26" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="22">
         <v>190</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="22">
         <v>1</v>
       </c>
       <c r="H26" s="14" t="s">
@@ -3134,13 +3136,13 @@
       <c r="D27" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="22">
         <v>310</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="22">
         <v>3</v>
       </c>
       <c r="H27" s="14" t="s">
@@ -3160,13 +3162,13 @@
       <c r="D28" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="22">
         <v>290</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="22">
         <v>2</v>
       </c>
       <c r="H28" s="14" t="s">
@@ -3186,13 +3188,13 @@
       <c r="D29" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="22">
         <v>340</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G29" s="22">
         <v>2</v>
       </c>
       <c r="H29" s="14" t="s">
@@ -3212,13 +3214,13 @@
       <c r="D30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="22">
         <v>760</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="22">
         <v>5</v>
       </c>
       <c r="H30" s="14" t="s">
@@ -3238,13 +3240,13 @@
       <c r="D31" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="22">
         <v>260</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="22">
         <v>2</v>
       </c>
       <c r="H31" s="14" t="s">
@@ -3264,13 +3266,13 @@
       <c r="D32" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="22">
         <v>420</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="22">
         <v>3</v>
       </c>
       <c r="H32" s="14" t="s">
@@ -3290,13 +3292,13 @@
       <c r="D33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="22">
         <v>120</v>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="22">
         <v>1</v>
       </c>
       <c r="H33" s="14" t="s">
@@ -3316,13 +3318,13 @@
       <c r="D34" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="22">
         <v>300</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="22">
         <v>3</v>
       </c>
       <c r="H34" s="14" t="s">
@@ -3345,10 +3347,10 @@
       <c r="E35" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="22">
         <v>180</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="22">
         <v>1</v>
       </c>
       <c r="H35" s="14" t="s">
@@ -3371,10 +3373,10 @@
       <c r="E36" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="22">
         <v>220</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="22">
         <v>2</v>
       </c>
       <c r="H36" s="14" t="s">
@@ -3397,10 +3399,10 @@
       <c r="E37" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F37" s="22">
         <v>90</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="22">
         <v>1</v>
       </c>
       <c r="H37" s="14" t="s">
@@ -3420,13 +3422,13 @@
       <c r="D38" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="22">
         <v>280</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="22">
         <v>2</v>
       </c>
       <c r="H38" s="14" t="s">
@@ -3449,10 +3451,10 @@
       <c r="E39" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="22">
         <v>250</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="22">
         <v>2</v>
       </c>
       <c r="H39" s="14" t="s">
@@ -3475,10 +3477,10 @@
       <c r="E40" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40" s="22">
         <v>520</v>
       </c>
-      <c r="G40" s="21">
+      <c r="G40" s="22">
         <v>4</v>
       </c>
       <c r="H40" s="14" t="s">
@@ -3501,10 +3503,10 @@
       <c r="E41" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="22">
         <v>340</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="22">
         <v>2</v>
       </c>
       <c r="H41" s="14" t="s">
@@ -3527,10 +3529,10 @@
       <c r="E42" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="22">
         <v>260</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="22">
         <v>2</v>
       </c>
       <c r="H42" s="14" t="s">
@@ -3553,10 +3555,10 @@
       <c r="E43" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="22">
         <v>150</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="22">
         <v>1</v>
       </c>
       <c r="H43" s="14" t="s">
@@ -3579,10 +3581,10 @@
       <c r="E44" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="22">
         <v>420</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="22">
         <v>3</v>
       </c>
       <c r="H44" s="14" t="s">
@@ -3605,10 +3607,10 @@
       <c r="E45" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="22">
         <v>280</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="22">
         <v>2</v>
       </c>
       <c r="H45" s="14" t="s">
@@ -3631,10 +3633,10 @@
       <c r="E46" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F46" s="22">
         <v>560</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="22">
         <v>4</v>
       </c>
       <c r="H46" s="14" t="s">
@@ -3657,10 +3659,10 @@
       <c r="E47" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="22">
         <v>210</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="22">
         <v>1</v>
       </c>
       <c r="H47" s="14" t="s">
@@ -3683,10 +3685,10 @@
       <c r="E48" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="22">
         <v>480</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="22">
         <v>4</v>
       </c>
       <c r="H48" s="14" t="s">
@@ -3709,10 +3711,10 @@
       <c r="E49" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="22">
         <v>180</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="22">
         <v>1</v>
       </c>
       <c r="H49" s="14" t="s">
@@ -3735,10 +3737,10 @@
       <c r="E50" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="22">
         <v>300</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="22">
         <v>2</v>
       </c>
       <c r="H50" s="14" t="s">
@@ -3761,10 +3763,10 @@
       <c r="E51" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="21">
+      <c r="F51" s="22">
         <v>330</v>
       </c>
-      <c r="G51" s="21">
+      <c r="G51" s="22">
         <v>3</v>
       </c>
       <c r="H51" s="14" t="s">
@@ -3787,10 +3789,10 @@
       <c r="E52" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="22">
         <v>170</v>
       </c>
-      <c r="G52" s="21">
+      <c r="G52" s="22">
         <v>1</v>
       </c>
       <c r="H52" s="14" t="s">
@@ -3813,10 +3815,10 @@
       <c r="E53" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="21">
+      <c r="F53" s="22">
         <v>360</v>
       </c>
-      <c r="G53" s="21">
+      <c r="G53" s="22">
         <v>3</v>
       </c>
       <c r="H53" s="14" t="s">
@@ -3839,10 +3841,10 @@
       <c r="E54" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="21">
+      <c r="F54" s="22">
         <v>520</v>
       </c>
-      <c r="G54" s="21">
+      <c r="G54" s="22">
         <v>4</v>
       </c>
       <c r="H54" s="14" t="s">
@@ -3865,10 +3867,10 @@
       <c r="E55" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="21">
+      <c r="F55" s="22">
         <v>290</v>
       </c>
-      <c r="G55" s="21">
+      <c r="G55" s="22">
         <v>2</v>
       </c>
       <c r="H55" s="14" t="s">
@@ -3891,10 +3893,10 @@
       <c r="E56" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="21">
+      <c r="F56" s="22">
         <v>420</v>
       </c>
-      <c r="G56" s="21">
+      <c r="G56" s="22">
         <v>3</v>
       </c>
       <c r="H56" s="14" t="s">
@@ -3917,10 +3919,10 @@
       <c r="E57" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="21">
+      <c r="F57" s="22">
         <v>620</v>
       </c>
-      <c r="G57" s="21">
+      <c r="G57" s="22">
         <v>5</v>
       </c>
       <c r="H57" s="14" t="s">
@@ -3943,10 +3945,10 @@
       <c r="E58" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="21">
+      <c r="F58" s="22">
         <v>240</v>
       </c>
-      <c r="G58" s="21">
+      <c r="G58" s="22">
         <v>2</v>
       </c>
       <c r="H58" s="14" t="s">
@@ -3966,13 +3968,13 @@
       <c r="D59" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="22">
         <v>310</v>
       </c>
-      <c r="G59" s="21">
+      <c r="G59" s="22">
         <v>3</v>
       </c>
       <c r="H59" s="14" t="s">
@@ -3995,10 +3997,10 @@
       <c r="E60" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="21">
+      <c r="F60" s="22">
         <v>140</v>
       </c>
-      <c r="G60" s="21">
+      <c r="G60" s="22">
         <v>1</v>
       </c>
       <c r="H60" s="14" t="s">
@@ -4021,10 +4023,10 @@
       <c r="E61" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F61" s="21">
+      <c r="F61" s="22">
         <v>120</v>
       </c>
-      <c r="G61" s="21">
+      <c r="G61" s="22">
         <v>1</v>
       </c>
       <c r="H61" s="14" t="s">
@@ -4044,13 +4046,13 @@
       <c r="D62" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="22">
         <v>320</v>
       </c>
-      <c r="G62" s="21">
+      <c r="G62" s="22">
         <v>2</v>
       </c>
       <c r="H62" s="14" t="s">
@@ -4070,13 +4072,13 @@
       <c r="D63" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="22">
         <v>680</v>
       </c>
-      <c r="G63" s="21">
+      <c r="G63" s="22">
         <v>4</v>
       </c>
       <c r="H63" s="14" t="s">
@@ -4096,13 +4098,13 @@
       <c r="D64" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="22">
         <v>540</v>
       </c>
-      <c r="G64" s="21">
+      <c r="G64" s="22">
         <v>4</v>
       </c>
       <c r="H64" s="14" t="s">
@@ -4122,13 +4124,13 @@
       <c r="D65" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="22">
         <v>300</v>
       </c>
-      <c r="G65" s="21">
+      <c r="G65" s="22">
         <v>2</v>
       </c>
       <c r="H65" s="14" t="s">
@@ -4148,13 +4150,13 @@
       <c r="D66" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="22">
         <v>130</v>
       </c>
-      <c r="G66" s="21">
+      <c r="G66" s="22">
         <v>1</v>
       </c>
       <c r="H66" s="14" t="s">
@@ -4174,13 +4176,13 @@
       <c r="D67" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="22">
         <v>240</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="22">
         <v>2</v>
       </c>
       <c r="H67" s="14" t="s">
@@ -4200,13 +4202,13 @@
       <c r="D68" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F68" s="21">
+      <c r="F68" s="22">
         <v>90</v>
       </c>
-      <c r="G68" s="21">
+      <c r="G68" s="22">
         <v>1</v>
       </c>
       <c r="H68" s="14" t="s">
@@ -4226,13 +4228,13 @@
       <c r="D69" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F69" s="21">
+      <c r="F69" s="22">
         <v>260</v>
       </c>
-      <c r="G69" s="21">
+      <c r="G69" s="22">
         <v>2</v>
       </c>
       <c r="H69" s="14" t="s">
@@ -4252,13 +4254,13 @@
       <c r="D70" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="21">
+      <c r="F70" s="22">
         <v>220</v>
       </c>
-      <c r="G70" s="21">
+      <c r="G70" s="22">
         <v>2</v>
       </c>
       <c r="H70" s="14" t="s">
@@ -4278,13 +4280,13 @@
       <c r="D71" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F71" s="21">
+      <c r="F71" s="22">
         <v>280</v>
       </c>
-      <c r="G71" s="21">
+      <c r="G71" s="22">
         <v>2</v>
       </c>
       <c r="H71" s="14" t="s">
@@ -4304,13 +4306,13 @@
       <c r="D72" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F72" s="21">
+      <c r="F72" s="22">
         <v>480</v>
       </c>
-      <c r="G72" s="21">
+      <c r="G72" s="22">
         <v>3</v>
       </c>
       <c r="H72" s="14" t="s">
@@ -4330,13 +4332,13 @@
       <c r="D73" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F73" s="21">
+      <c r="F73" s="22">
         <v>340</v>
       </c>
-      <c r="G73" s="21">
+      <c r="G73" s="22">
         <v>3</v>
       </c>
       <c r="H73" s="14" t="s">
@@ -4356,13 +4358,13 @@
       <c r="D74" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F74" s="21">
+      <c r="F74" s="22">
         <v>170</v>
       </c>
-      <c r="G74" s="21">
+      <c r="G74" s="22">
         <v>1</v>
       </c>
       <c r="H74" s="14" t="s">
@@ -4385,10 +4387,10 @@
       <c r="E75" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F75" s="21">
+      <c r="F75" s="22">
         <v>300</v>
       </c>
-      <c r="G75" s="21">
+      <c r="G75" s="22">
         <v>3</v>
       </c>
       <c r="H75" s="14" t="s">
@@ -4411,10 +4413,10 @@
       <c r="E76" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F76" s="21">
+      <c r="F76" s="22">
         <v>160</v>
       </c>
-      <c r="G76" s="21">
+      <c r="G76" s="22">
         <v>1</v>
       </c>
       <c r="H76" s="14" t="s">
@@ -4434,13 +4436,13 @@
       <c r="D77" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F77" s="21">
+      <c r="F77" s="22">
         <v>380</v>
       </c>
-      <c r="G77" s="21">
+      <c r="G77" s="22">
         <v>3</v>
       </c>
       <c r="H77" s="14" t="s">
@@ -4460,13 +4462,13 @@
       <c r="D78" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F78" s="21">
+      <c r="F78" s="22">
         <v>220</v>
       </c>
-      <c r="G78" s="21">
+      <c r="G78" s="22">
         <v>2</v>
       </c>
       <c r="H78" s="14" t="s">
@@ -4489,10 +4491,10 @@
       <c r="E79" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F79" s="21">
+      <c r="F79" s="22">
         <v>80</v>
       </c>
-      <c r="G79" s="21">
+      <c r="G79" s="22">
         <v>1</v>
       </c>
       <c r="H79" s="14" t="s">
@@ -4512,13 +4514,13 @@
       <c r="D80" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F80" s="21">
+      <c r="F80" s="22">
         <v>150</v>
       </c>
-      <c r="G80" s="21">
+      <c r="G80" s="22">
         <v>1</v>
       </c>
       <c r="H80" s="14" t="s">
@@ -4538,13 +4540,13 @@
       <c r="D81" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F81" s="21">
+      <c r="F81" s="22">
         <v>210</v>
       </c>
-      <c r="G81" s="21">
+      <c r="G81" s="22">
         <v>2</v>
       </c>
       <c r="H81" s="14" t="s">
@@ -4564,13 +4566,13 @@
       <c r="D82" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F82" s="21">
+      <c r="F82" s="22">
         <v>260</v>
       </c>
-      <c r="G82" s="21">
+      <c r="G82" s="22">
         <v>2</v>
       </c>
       <c r="H82" s="14" t="s">
@@ -4593,10 +4595,10 @@
       <c r="E83" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F83" s="21">
+      <c r="F83" s="22">
         <v>190</v>
       </c>
-      <c r="G83" s="21">
+      <c r="G83" s="22">
         <v>1</v>
       </c>
       <c r="H83" s="14" t="s">
@@ -4619,10 +4621,10 @@
       <c r="E84" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F84" s="21">
+      <c r="F84" s="22">
         <v>430</v>
       </c>
-      <c r="G84" s="21">
+      <c r="G84" s="22">
         <v>3</v>
       </c>
       <c r="H84" s="14" t="s">
@@ -4645,10 +4647,10 @@
       <c r="E85" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F85" s="21">
+      <c r="F85" s="22">
         <v>620</v>
       </c>
-      <c r="G85" s="21">
+      <c r="G85" s="22">
         <v>4</v>
       </c>
       <c r="H85" s="14" t="s">
@@ -4671,10 +4673,10 @@
       <c r="E86" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F86" s="21">
+      <c r="F86" s="22">
         <v>260</v>
       </c>
-      <c r="G86" s="21">
+      <c r="G86" s="22">
         <v>2</v>
       </c>
       <c r="H86" s="14" t="s">
@@ -4697,10 +4699,10 @@
       <c r="E87" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F87" s="21">
+      <c r="F87" s="22">
         <v>540</v>
       </c>
-      <c r="G87" s="21">
+      <c r="G87" s="22">
         <v>4</v>
       </c>
       <c r="H87" s="14" t="s">
@@ -4723,10 +4725,10 @@
       <c r="E88" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F88" s="21">
+      <c r="F88" s="22">
         <v>330</v>
       </c>
-      <c r="G88" s="21">
+      <c r="G88" s="22">
         <v>2</v>
       </c>
       <c r="H88" s="14" t="s">
@@ -4749,10 +4751,10 @@
       <c r="E89" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F89" s="21">
+      <c r="F89" s="22">
         <v>220</v>
       </c>
-      <c r="G89" s="21">
+      <c r="G89" s="22">
         <v>2</v>
       </c>
       <c r="H89" s="14" t="s">
@@ -4775,10 +4777,10 @@
       <c r="E90" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F90" s="21">
+      <c r="F90" s="22">
         <v>370</v>
       </c>
-      <c r="G90" s="21">
+      <c r="G90" s="22">
         <v>3</v>
       </c>
       <c r="H90" s="14" t="s">
@@ -4801,10 +4803,10 @@
       <c r="E91" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="21">
+      <c r="F91" s="22">
         <v>290</v>
       </c>
-      <c r="G91" s="21">
+      <c r="G91" s="22">
         <v>2</v>
       </c>
       <c r="H91" s="14" t="s">
@@ -4827,10 +4829,10 @@
       <c r="E92" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="21">
+      <c r="F92" s="22">
         <v>140</v>
       </c>
-      <c r="G92" s="21">
+      <c r="G92" s="22">
         <v>1</v>
       </c>
       <c r="H92" s="14" t="s">
@@ -4853,10 +4855,10 @@
       <c r="E93" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F93" s="21">
+      <c r="F93" s="22">
         <v>310</v>
       </c>
-      <c r="G93" s="21">
+      <c r="G93" s="22">
         <v>2</v>
       </c>
       <c r="H93" s="14" t="s">
@@ -4876,13 +4878,13 @@
       <c r="D94" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F94" s="21">
+      <c r="F94" s="22">
         <v>360</v>
       </c>
-      <c r="G94" s="21">
+      <c r="G94" s="22">
         <v>3</v>
       </c>
       <c r="H94" s="14" t="s">
@@ -4902,13 +4904,13 @@
       <c r="D95" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F95" s="21">
+      <c r="F95" s="22">
         <v>300</v>
       </c>
-      <c r="G95" s="21">
+      <c r="G95" s="22">
         <v>2</v>
       </c>
       <c r="H95" s="14" t="s">
@@ -4928,13 +4930,13 @@
       <c r="D96" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F96" s="21">
+      <c r="F96" s="22">
         <v>420</v>
       </c>
-      <c r="G96" s="21">
+      <c r="G96" s="22">
         <v>3</v>
       </c>
       <c r="H96" s="14" t="s">
@@ -4954,13 +4956,13 @@
       <c r="D97" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F97" s="21">
+      <c r="F97" s="22">
         <v>280</v>
       </c>
-      <c r="G97" s="21">
+      <c r="G97" s="22">
         <v>3</v>
       </c>
       <c r="H97" s="14" t="s">
@@ -4980,13 +4982,13 @@
       <c r="D98" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F98" s="21">
+      <c r="F98" s="22">
         <v>240</v>
       </c>
-      <c r="G98" s="21">
+      <c r="G98" s="22">
         <v>2</v>
       </c>
       <c r="H98" s="14" t="s">
@@ -5006,13 +5008,13 @@
       <c r="D99" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F99" s="21">
+      <c r="F99" s="22">
         <v>190</v>
       </c>
-      <c r="G99" s="21">
+      <c r="G99" s="22">
         <v>1</v>
       </c>
       <c r="H99" s="14" t="s">
@@ -5032,13 +5034,13 @@
       <c r="D100" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F100" s="21">
+      <c r="F100" s="22">
         <v>340</v>
       </c>
-      <c r="G100" s="21">
+      <c r="G100" s="22">
         <v>3</v>
       </c>
       <c r="H100" s="14" t="s">
@@ -5058,13 +5060,13 @@
       <c r="D101" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F101" s="21">
+      <c r="F101" s="22">
         <v>520</v>
       </c>
-      <c r="G101" s="21">
+      <c r="G101" s="22">
         <v>4</v>
       </c>
       <c r="H101" s="14" t="s">
@@ -5084,13 +5086,13 @@
       <c r="D102" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E102" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F102" s="21">
+      <c r="F102" s="22">
         <v>110</v>
       </c>
-      <c r="G102" s="21">
+      <c r="G102" s="22">
         <v>1</v>
       </c>
       <c r="H102" s="14" t="s">
@@ -5098,28 +5100,28 @@
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:8">
-      <c r="A103" s="15" t="s">
+      <c r="A103" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="B103" s="16" t="s">
+      <c r="B103" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D103" s="16" t="s">
+      <c r="D103" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E103" s="16" t="s">
+      <c r="E103" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F103" s="22">
+      <c r="F103" s="23">
         <v>460</v>
       </c>
-      <c r="G103" s="22">
+      <c r="G103" s="23">
         <v>4</v>
       </c>
-      <c r="H103" s="19" t="s">
+      <c r="H103" s="20" t="s">
         <v>233</v>
       </c>
     </row>
@@ -5147,7 +5149,7 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="15" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5478,7 +5480,7 @@
       <c r="F13" s="13">
         <v>0.12</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="15" t="s">
         <v>52</v>
       </c>
       <c r="H13" s="14" t="s">
@@ -5634,7 +5636,7 @@
       <c r="F19" s="13">
         <v>0.14</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="15" t="s">
         <v>74</v>
       </c>
       <c r="H19" s="14" t="s">
@@ -5660,7 +5662,7 @@
       <c r="F20" s="13">
         <v>0.1</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="15" t="s">
         <v>52</v>
       </c>
       <c r="H20" s="14" t="s">
@@ -5720,28 +5722,28 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:8">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>0.1</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="20" t="s">
         <v>331</v>
       </c>
     </row>
